--- a/v3/OG0021/OG0021_ReadingQuiz.xlsx
+++ b/v3/OG0021/OG0021_ReadingQuiz.xlsx
@@ -3179,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>["forest.", "the", "into", "walks", "Milo"]</t>
+          <t>["the forest.", "into", "walks", "Milo"]</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>["Milo", "walks", "into", "the", "forest."]</t>
+          <t>["Milo", "walks", "into", "the forest."]</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -3535,11 +3535,11 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>the forest.</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -3559,90 +3559,64 @@
       <c r="H14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>forest.</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>exact_position</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Actor/action/result word order.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SECTION D</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SECTION D</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Diagnostics</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr"/>
-      <c r="H17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>attempt_sentence_gap</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B17" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>인물이 문제를 해결하려고 한 행동 문장을 순서대로 구성하는 연습이 필요합니다.</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
